--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -36,16 +36,22 @@
     <t xml:space="preserve">Atacama</t>
   </si>
   <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Caldera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freirina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego de Almagro</t>
   </si>
   <si>
     <t xml:space="preserve">Vallenar</t>
@@ -54,15 +60,9 @@
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tierra Amarilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,13 +502,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3302</v>
+        <v>3304</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3102</v>
+        <v>3303</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.19</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="4">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3303</v>
+        <v>3102</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.17</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="6">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3301</v>
+        <v>3201</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.56</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="7">
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3101</v>
+        <v>3202</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-2.11</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3201</v>
+        <v>3301</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.6</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-5.73</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3202</v>
+        <v>3103</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-8.94</v>
+        <v>-3.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.3</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.38</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.13</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.79</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.85</v>
+        <v>8.47</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.62</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.46</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.3</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3.32</v>
+        <v>-33.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-05 08:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
